--- a/Decks/Pé.xlsx
+++ b/Decks/Pé.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACB667E-4C7C-4B2C-ADFE-E3D75A93F8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B6C729-7BB1-4370-9F55-1A472B77320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="93">
   <si>
     <t>Função</t>
   </si>
@@ -875,9 +875,11 @@
       </c>
       <c r="B12" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D12" s="4" t="s">
         <v>78</v>
       </c>
@@ -1968,9 +1970,11 @@
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C91" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="D91" s="4" t="s">
         <v>83</v>
       </c>

--- a/Decks/Pé.xlsx
+++ b/Decks/Pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B6C729-7BB1-4370-9F55-1A472B77320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578362F-0F88-467C-93E2-13084A7BD50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
   <si>
     <t>Função</t>
   </si>
@@ -741,9 +741,11 @@
       </c>
       <c r="B2" s="5" t="b">
         <f>C2&lt;&gt;D2</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
@@ -847,9 +849,11 @@
       </c>
       <c r="B10" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="D10" s="4" t="s">
         <v>68</v>
       </c>
@@ -920,9 +924,11 @@
       </c>
       <c r="B15" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C15" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D15" s="4" t="s">
         <v>12</v>
       </c>
@@ -933,9 +939,11 @@
       </c>
       <c r="B16" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C16" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
       </c>
@@ -946,9 +954,11 @@
       </c>
       <c r="B17" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C17" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D17" s="4" t="s">
         <v>12</v>
       </c>
@@ -959,9 +969,11 @@
       </c>
       <c r="B18" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C18" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
       </c>
@@ -972,9 +984,11 @@
       </c>
       <c r="B19" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C19" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D19" s="4" t="s">
         <v>12</v>
       </c>
@@ -985,9 +999,11 @@
       </c>
       <c r="B20" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C20" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
       </c>
@@ -998,9 +1014,11 @@
       </c>
       <c r="B21" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D21" s="4" t="s">
         <v>12</v>
       </c>
@@ -1011,9 +1029,11 @@
       </c>
       <c r="B22" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C22" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
       </c>
@@ -1024,9 +1044,11 @@
       </c>
       <c r="B23" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C23" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
       </c>
@@ -1037,9 +1059,11 @@
       </c>
       <c r="B24" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C24" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
       </c>
@@ -1050,9 +1074,11 @@
       </c>
       <c r="B25" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C25" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
       </c>
@@ -1063,9 +1089,11 @@
       </c>
       <c r="B26" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C26" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1076,9 +1104,11 @@
       </c>
       <c r="B27" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C27" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D27" s="4" t="s">
         <v>12</v>
       </c>
@@ -1089,9 +1119,11 @@
       </c>
       <c r="B28" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C28" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
       </c>
@@ -1102,9 +1134,11 @@
       </c>
       <c r="B29" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C29" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
       </c>
@@ -1115,9 +1149,11 @@
       </c>
       <c r="B30" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C30" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
       </c>
@@ -1128,9 +1164,11 @@
       </c>
       <c r="B31" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C31" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D31" s="4" t="s">
         <v>13</v>
       </c>
@@ -1141,9 +1179,11 @@
       </c>
       <c r="B32" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C32" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D32" s="4" t="s">
         <v>13</v>
       </c>
@@ -1154,9 +1194,11 @@
       </c>
       <c r="B33" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C33" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D33" s="4" t="s">
         <v>13</v>
       </c>
@@ -1167,9 +1209,11 @@
       </c>
       <c r="B34" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C34" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D34" s="4" t="s">
         <v>13</v>
       </c>
@@ -1180,9 +1224,11 @@
       </c>
       <c r="B35" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C35" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D35" s="4" t="s">
         <v>13</v>
       </c>
@@ -1193,9 +1239,11 @@
       </c>
       <c r="B36" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C36" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D36" s="4" t="s">
         <v>13</v>
       </c>
@@ -1206,9 +1254,11 @@
       </c>
       <c r="B37" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C37" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D37" s="4" t="s">
         <v>13</v>
       </c>
@@ -1826,9 +1876,11 @@
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
-        <v>1</v>
-      </c>
-      <c r="C81" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D81" s="4" t="s">
         <v>53</v>
       </c>

--- a/Decks/Pé.xlsx
+++ b/Decks/Pé.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578362F-0F88-467C-93E2-13084A7BD50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2500187-6C14-43AA-890B-C65351959DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="93">
   <si>
     <t>Função</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Skullclamp</t>
   </si>
   <si>
-    <t>Psychotrope Thallid</t>
-  </si>
-  <si>
     <t>Insidious Fungus</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>Nullmage Shepherd</t>
+  </si>
+  <si>
+    <t>Evolutionary Leap</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -801,7 +801,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -814,7 +814,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -827,7 +827,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -840,7 +840,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -897,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,9 +1269,11 @@
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C38" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D38" s="4" t="s">
         <v>16</v>
       </c>
@@ -1326,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,9 +1353,11 @@
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C44" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D44" s="4" t="s">
         <v>33</v>
       </c>
@@ -1367,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1397,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1412,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1442,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1457,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1472,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,7 +1492,7 @@
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,9 +1501,11 @@
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C54" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="D54" s="4" t="s">
         <v>32</v>
       </c>
@@ -1514,7 +1520,7 @@
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,7 +1533,7 @@
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,7 +1546,7 @@
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,7 +1559,7 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,7 +1572,7 @@
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1591,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>39</v>
@@ -1606,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,11 +1652,13 @@
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
-        <v>1</v>
-      </c>
-      <c r="C65" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="D65" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1663,7 +1671,7 @@
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1691,7 +1699,7 @@
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1703,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,11 +1738,13 @@
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C71" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="D71" s="4" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1834,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1879,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1894,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1925,7 +1935,7 @@
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,10 +1977,10 @@
         <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1997,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2013,7 +2023,7 @@
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2025,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2056,7 +2066,7 @@
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,7 +2094,7 @@
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2097,7 +2107,7 @@
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2124,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,11 +2172,13 @@
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C101" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="D101" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Pé.xlsx
+++ b/Decks/Pé.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2500187-6C14-43AA-890B-C65351959DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B55578-5E8C-466E-B958-E95CCCAEAA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="93">
   <si>
     <t>Função</t>
   </si>
@@ -1542,9 +1542,11 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C57" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="D57" s="4" t="s">
         <v>42</v>
       </c>
@@ -1581,9 +1583,11 @@
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C60" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D60" s="4" t="s">
         <v>31</v>
       </c>
@@ -1594,10 +1598,10 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>39</v>
@@ -1626,7 +1630,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C63" s="4"/>
+      <c r="C63" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="D63" s="4" t="s">
         <v>17</v>
       </c>
